--- a/lucas/import_data/utility/observation/excel/provider.xlsx
+++ b/lucas/import_data/utility/observation/excel/provider.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="106">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -308,6 +308,36 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.bruker.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">human interpreter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">human interpter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">human sensing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Human interpretation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">european environment agency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eu-eea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">European Environment Agency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.eea.europa.eu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">info@eea.europa.eu</t>
   </si>
 </sst>
 </file>
@@ -317,7 +347,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -356,6 +386,13 @@
     <font>
       <sz val="11.5"/>
       <color rgb="FF151137"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -403,7 +440,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -425,6 +462,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -508,37 +549,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -611,13 +652,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="37.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="25.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="28.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="25.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18.82"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="18.22"/>
   </cols>
@@ -997,11 +1039,49 @@
         <v>95</v>
       </c>
     </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" display="info@metrohm.com"/>
     <hyperlink ref="G10" r:id="rId2" display="thomas@xspectre.com"/>
     <hyperlink ref="E19" r:id="rId3" display="https://www.buchi.com"/>
+    <hyperlink ref="E23" r:id="rId4" display="https://www.eea.europa.eu"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
